--- a/DatasetUnical/ResultsClingcon/truecons-trueprod/analysis_truecons-trueprod.xlsx
+++ b/DatasetUnical/ResultsClingcon/truecons-trueprod/analysis_truecons-trueprod.xlsx
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -597,7 +597,7 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>6.39</v>
+        <v>6.38</v>
       </c>
       <c r="S3" s="1">
         <f>T3/V$1</f>
@@ -636,7 +636,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>6.67</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -651,7 +651,7 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>6.67</v>
+        <v>0</v>
       </c>
       <c r="S4" s="1">
         <f>T4/V$1</f>
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -695,7 +695,7 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>4.06</v>
+        <v>6.82</v>
       </c>
       <c r="S5" s="1">
         <f>T5/V$1</f>
@@ -724,7 +724,7 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>6.9</v>
+        <v>0.95</v>
       </c>
       <c r="S6" s="1">
         <f>T6/V$1</f>
@@ -778,7 +778,7 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -793,7 +793,7 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="S7" s="1">
         <f>T7/V$1</f>
@@ -810,8 +810,8 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 1 (Time: 0.008s).
-vFinalCharge(360). vE_SinitPercentage(1000). vCharge("2023-08-21","0:00:00",0). vCharge("2023-08-21","10:00:00",0). vCharge("2023-08-21","11:00:00",0). vCharge("2023-08-21","12:00:00",0). vCharge("2023-08-21","13:00:00",0). vCharge("2023-08-21","14:00:00",0). vCharge("2023-08-21","15:00:00",0). vCharge("2023-08-21","16:00:00",0). vCharge("2023-08-21","17:00:00",0). vCharge("2023-08-21","18:00:00",0). vCharge("2023-08-21","19:00:00",0). vCharge("2023-08-21","1:00:00",0). vCharge("2023-08-21","20:00:00",0). vCharge("2023-08-21","21:00:00",0). vCharge("2023-08-21","22:00:00",0). vCharge("2023-08-21","23:00:00",0). vCharge("2023-08-21","2:00:00",0). vCharge("2023-08-21","3:00:00",0). vCharge("2023-08-21","4:00:00",0). vCharge("2023-08-21","5:00:00",0). vCharge("2023-08-21","6:00:00",0). vCharge("2023-08-21","7:00:00",0). vCharge("2023-08-21","8:00:00",0). vCharge("2023-08-21","9:00:00",0). vDischarge("2023-08-21","0:00:00",1). vDischarge("2023-08-21","10:00:00",0). vDischarge("2023-08-21","11:00:00",0). vDischarge("2023-08-21","12:00:00",0). vDischarge("2023-08-21","13:00:00",0). vDischarge("2023-08-21","14:00:00",0). vDischarge("2023-08-21","15:00:00",0). vDischarge("2023-08-21","16:00:00",0). vDischarge("2023-08-21","17:00:00",0). vDischarge("2023-08-21","18:00:00",0). vDischarge("2023-08-21","19:00:00",1049). vDischarge("2023-08-21","1:00:00",0). vDischarge("2023-08-21","20:00:00",1015). vDischarge("2023-08-21","21:00:00",709). vDischarge("2023-08-21","22:00:00",0). vDischarge("2023-08-21","23:00:00",189). vDischarge("2023-08-21","2:00:00",276). vDischarge("2023-08-21","3:00:00",0). vDischarge("2023-08-21","4:00:00",0). vDischarge("2023-08-21","5:00:00",1). vDischarge("2023-08-21","6:00:00",0). vDischarge("2023-08-21","7:00:00",0). vDischarge("2023-08-21","8:00:00",0). vDischarge("2023-08-21","9:00:00",0). vFeed_in("2023-08-21","0:00:00",0). vFeed_in("2023-08-21","10:00:00",2449). vFeed_in("2023-08-21","11:00:00",2981). vFeed_in("2023-08-21","12:00:00",3158). vFeed_in("2023-08-21","13:00:00",3160). vFeed_in("2023-08-21","14:00:00",2952). vFeed_in("2023-08-21","15:00:00",2464). vFeed_in("2023-08-21","16:00:00",1534). vFeed_in("2023-08-21","17:00:00",0). vFeed_in("2023-08-21","18:00:00",0). vFeed_in("2023-08-21","19:00:00",0). vFeed_in("2023-08-21","1:00:00",0). vFeed_in("2023-08-21","20:00:00",0). vFeed_in("2023-08-21","21:00:00",0). vFeed_in("2023-08-21","22:00:00",0). vFeed_in("2023-08-21","23:00:00",0). vFeed_in("2023-08-21","2:00:00",0). vFeed_in("2023-08-21","3:00:00",0). vFeed_in("2023-08-21","4:00:00",0). vFeed_in("2023-08-21","5:00:00",0). vFeed_in("2023-08-21","6:00:00",0). vFeed_in("2023-08-21","7:00:00",0). vFeed_in("2023-08-21","8:00:00",712). vFeed_in("2023-08-21","9:00:00",1414). vFrom_grid("2023-08-21","0:00:00",639). vFrom_grid("2023-08-21","10:00:00",0). vFrom_grid("2023-08-21","11:00:00",0). vFrom_grid("2023-08-21","12:00:00",0). vFrom_grid("2023-08-21","13:00:00",0). vFrom_grid("2023-08-21","14:00:00",0). vFrom_grid("2023-08-21","15:00:00",0). vFrom_grid("2023-08-21","16:00:00",0). vFrom_grid("2023-08-21","17:00:00",441). vFrom_grid("2023-08-21","18:00:00",943). vFrom_grid("2023-08-21","19:00:00",0). vFrom_grid("2023-08-21","1:00:00",667). vFrom_grid("2023-08-21","20:00:00",0). vFrom_grid("2023-08-21","21:00:00",500). vFrom_grid("2023-08-21","22:00:00",860). vFrom_grid("2023-08-21","23:00:00",654). vFrom_grid("2023-08-21","2:00:00",406). vFrom_grid("2023-08-21","3:00:00",690). vFrom_grid("2023-08-21","4:00:00",670). vFrom_grid("2023-08-21","5:00:00",549). vFrom_grid("2023-08-21","6:00:00",655). vFrom_grid("2023-08-21","7:00:00",204). vFrom_grid("2023-08-21","8:00:00",0). vFrom_grid("2023-08-21","9:00:00",0). vP_L("2023-08-21","0:00:00",640). vP_L("2023-08-21","10:00:00",1060). vP_L("2023-08-21","11:00:00",978). vP_L("2023-08-21","12:00:00",1198). vP_L("2023-08-21","13:00:00",1181). vP_L("2023-08-21","14:00:00",1202). vP_L("2023-08-21","15:00:00",1180). vP_L("2023-08-21","16:00:00",1196). vP_L("2023-08-21","17:00:00",954). vP_L("2023-08-21","18:00:00",1196). vP_L("2023-08-21","19:00:00",1087). vP_L("2023-08-21","1:00:00",667). vP_L("2023-08-21","20:00:00",1015). vP_L("2023-08-21","21:00:00",1209). vP_L("2023-08-21","22:00:00",860). vP_L("2023-08-21","23:00:00",843). vP_L("2023-08-21","2:00:00",682). vP_L("2023-08-21","3:00:00",690). vP_L("2023-08-21","4:00:00",670). vP_L("2023-08-21","5:00:00",550). vP_L("2023-08-21","6:00:00",667). vP_L("2023-08-21","7:00:00",633). vP_L("2023-08-21","8:00:00",873). vP_L("2023-08-21","9:00:00",1294). vP_PV("2023-08-21","0:00:00",0). vP_PV("2023-08-21","10:00:00",3509). vP_PV("2023-08-21","11:00:00",3959). vP_PV("2023-08-21","12:00:00",4356). vP_PV("2023-08-21","13:00:00",4341). vP_PV("2023-08-21","14:00:00",4154). vP_PV("2023-08-21","15:00:00",3644). vP_PV("2023-08-21","16:00:00",2730). vP_PV("2023-08-21","17:00:00",513). vP_PV("2023-08-21","18:00:00",253). vP_PV("2023-08-21","19:00:00",38). vP_PV("2023-08-21","1:00:00",0). vP_PV("2023-08-21","20:00:00",0). vP_PV("2023-08-21","21:00:00",0). vP_PV("2023-08-21","22:00:00",0). vP_PV("2023-08-21","23:00:00",0). vP_PV("2023-08-21","2:00:00",0). vP_PV("2023-08-21","3:00:00",0). vP_PV("2023-08-21","4:00:00",0). vP_PV("2023-08-21","5:00:00",0). vP_PV("2023-08-21","6:00:00",12). vP_PV("2023-08-21","7:00:00",429). vP_PV("2023-08-21","8:00:00",1585). vP_PV("2023-08-21","9:00:00",2708).
+          <t xml:space="preserve"> 1 (Time: 0.010s).
+vFinalCharge(3600). vE_SinitPercentage(10000). vCharge("2023-08-21","0:00:00",0). vCharge("2023-08-21","10:00:00",483). vCharge("2023-08-21","11:00:00",37). vCharge("2023-08-21","12:00:00",0). vCharge("2023-08-21","13:00:00",483). vCharge("2023-08-21","14:00:00",515). vCharge("2023-08-21","15:00:00",0). vCharge("2023-08-21","16:00:00",515). vCharge("2023-08-21","17:00:00",0). vCharge("2023-08-21","18:00:00",0). vCharge("2023-08-21","19:00:00",0). vCharge("2023-08-21","1:00:00",0). vCharge("2023-08-21","20:00:00",0). vCharge("2023-08-21","21:00:00",0). vCharge("2023-08-21","22:00:00",0). vCharge("2023-08-21","23:00:00",0). vCharge("2023-08-21","2:00:00",0). vCharge("2023-08-21","3:00:00",0). vCharge("2023-08-21","4:00:00",0). vCharge("2023-08-21","5:00:00",0). vCharge("2023-08-21","6:00:00",0). vCharge("2023-08-21","7:00:00",0). vCharge("2023-08-21","8:00:00",653). vCharge("2023-08-21","9:00:00",1). vDischarge("2023-08-21","0:00:00",2). vDischarge("2023-08-21","10:00:00",0). vDischarge("2023-08-21","11:00:00",0). vDischarge("2023-08-21","12:00:00",0). vDischarge("2023-08-21","13:00:00",0). vDischarge("2023-08-21","14:00:00",0). vDischarge("2023-08-21","15:00:00",0). vDischarge("2023-08-21","16:00:00",0). vDischarge("2023-08-21","17:00:00",0). vDischarge("2023-08-21","18:00:00",0). vDischarge("2023-08-21","19:00:00",0). vDischarge("2023-08-21","1:00:00",667). vDischarge("2023-08-21","20:00:00",0). vDischarge("2023-08-21","21:00:00",0). vDischarge("2023-08-21","22:00:00",0). vDischarge("2023-08-21","23:00:00",0). vDischarge("2023-08-21","2:00:00",0). vDischarge("2023-08-21","3:00:00",595). vDischarge("2023-08-21","4:00:00",670). vDischarge("2023-08-21","5:00:00",550). vDischarge("2023-08-21","6:00:00",0). vDischarge("2023-08-21","7:00:00",203). vDischarge("2023-08-21","8:00:00",0). vDischarge("2023-08-21","9:00:00",0). vFeed_in("2023-08-21","0:00:00",0). vFeed_in("2023-08-21","10:00:00",1966). vFeed_in("2023-08-21","11:00:00",2944). vFeed_in("2023-08-21","12:00:00",3158). vFeed_in("2023-08-21","13:00:00",2677). vFeed_in("2023-08-21","14:00:00",2437). vFeed_in("2023-08-21","15:00:00",2464). vFeed_in("2023-08-21","16:00:00",1019). vFeed_in("2023-08-21","17:00:00",0). vFeed_in("2023-08-21","18:00:00",0). vFeed_in("2023-08-21","19:00:00",0). vFeed_in("2023-08-21","1:00:00",0). vFeed_in("2023-08-21","20:00:00",0). vFeed_in("2023-08-21","21:00:00",0). vFeed_in("2023-08-21","22:00:00",0). vFeed_in("2023-08-21","23:00:00",0). vFeed_in("2023-08-21","2:00:00",0). vFeed_in("2023-08-21","3:00:00",0). vFeed_in("2023-08-21","4:00:00",0). vFeed_in("2023-08-21","5:00:00",0). vFeed_in("2023-08-21","6:00:00",0). vFeed_in("2023-08-21","7:00:00",0). vFeed_in("2023-08-21","8:00:00",59). vFeed_in("2023-08-21","9:00:00",1413). vFrom_grid("2023-08-21","0:00:00",638). vFrom_grid("2023-08-21","10:00:00",0). vFrom_grid("2023-08-21","11:00:00",0). vFrom_grid("2023-08-21","12:00:00",0). vFrom_grid("2023-08-21","13:00:00",0). vFrom_grid("2023-08-21","14:00:00",0). vFrom_grid("2023-08-21","15:00:00",0). vFrom_grid("2023-08-21","16:00:00",0). vFrom_grid("2023-08-21","17:00:00",441). vFrom_grid("2023-08-21","18:00:00",943). vFrom_grid("2023-08-21","19:00:00",1049). vFrom_grid("2023-08-21","1:00:00",0). vFrom_grid("2023-08-21","20:00:00",1015). vFrom_grid("2023-08-21","21:00:00",1209). vFrom_grid("2023-08-21","22:00:00",860). vFrom_grid("2023-08-21","23:00:00",843). vFrom_grid("2023-08-21","2:00:00",682). vFrom_grid("2023-08-21","3:00:00",95). vFrom_grid("2023-08-21","4:00:00",0). vFrom_grid("2023-08-21","5:00:00",0). vFrom_grid("2023-08-21","6:00:00",655). vFrom_grid("2023-08-21","7:00:00",1). vFrom_grid("2023-08-21","8:00:00",0). vFrom_grid("2023-08-21","9:00:00",0). vP_L("2023-08-21","0:00:00",640). vP_L("2023-08-21","10:00:00",1060). vP_L("2023-08-21","11:00:00",978). vP_L("2023-08-21","12:00:00",1198). vP_L("2023-08-21","13:00:00",1181). vP_L("2023-08-21","14:00:00",1202). vP_L("2023-08-21","15:00:00",1180). vP_L("2023-08-21","16:00:00",1196). vP_L("2023-08-21","17:00:00",954). vP_L("2023-08-21","18:00:00",1196). vP_L("2023-08-21","19:00:00",1087). vP_L("2023-08-21","1:00:00",667). vP_L("2023-08-21","20:00:00",1015). vP_L("2023-08-21","21:00:00",1209). vP_L("2023-08-21","22:00:00",860). vP_L("2023-08-21","23:00:00",843). vP_L("2023-08-21","2:00:00",682). vP_L("2023-08-21","3:00:00",690). vP_L("2023-08-21","4:00:00",670). vP_L("2023-08-21","5:00:00",550). vP_L("2023-08-21","6:00:00",667). vP_L("2023-08-21","7:00:00",633). vP_L("2023-08-21","8:00:00",873). vP_L("2023-08-21","9:00:00",1294). vP_PV("2023-08-21","0:00:00",0). vP_PV("2023-08-21","10:00:00",3509). vP_PV("2023-08-21","11:00:00",3959). vP_PV("2023-08-21","12:00:00",4356). vP_PV("2023-08-21","13:00:00",4341). vP_PV("2023-08-21","14:00:00",4154). vP_PV("2023-08-21","15:00:00",3644). vP_PV("2023-08-21","16:00:00",2730). vP_PV("2023-08-21","17:00:00",513). vP_PV("2023-08-21","18:00:00",253). vP_PV("2023-08-21","19:00:00",38). vP_PV("2023-08-21","1:00:00",0). vP_PV("2023-08-21","20:00:00",0). vP_PV("2023-08-21","21:00:00",0). vP_PV("2023-08-21","22:00:00",0). vP_PV("2023-08-21","23:00:00",0). vP_PV("2023-08-21","2:00:00",0). vP_PV("2023-08-21","3:00:00",0). vP_PV("2023-08-21","4:00:00",0). vP_PV("2023-08-21","5:00:00",0). vP_PV("2023-08-21","6:00:00",12). vP_PV("2023-08-21","7:00:00",429). vP_PV("2023-08-21","8:00:00",1585). vP_PV("2023-08-21","9:00:00",2708).
 </t>
         </is>
       </c>
@@ -834,7 +834,7 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.01</v>
+        <v>5.5</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -849,7 +849,7 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>5.49</v>
+        <v>0</v>
       </c>
       <c r="S8" s="1">
         <f>T8/V$1</f>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.008</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="9">
@@ -939,7 +939,7 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -954,7 +954,7 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.04</v>
+        <v>0.01</v>
       </c>
       <c r="S10" s="1">
         <f>T10/V$1</f>
@@ -986,7 +986,7 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>6.53</v>
       </c>
       <c r="O11" t="n">
         <v>15.85</v>
@@ -995,7 +995,7 @@
         <v>8.73</v>
       </c>
       <c r="Q11" t="n">
-        <v>7.12</v>
+        <v>0.59</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1030,7 +1030,7 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="O12" t="n">
         <v>27.08</v>
@@ -1039,7 +1039,7 @@
         <v>12.94</v>
       </c>
       <c r="Q12" t="n">
-        <v>14.14</v>
+        <v>14.13</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1074,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>4.83</v>
       </c>
       <c r="O13" t="n">
         <v>35.09</v>
@@ -1083,7 +1083,7 @@
         <v>10.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>24.49</v>
+        <v>19.66</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1118,7 +1118,7 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>0.37</v>
       </c>
       <c r="O14" t="n">
         <v>39.59</v>
@@ -1127,7 +1127,7 @@
         <v>9.779999999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>29.81</v>
+        <v>29.44</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1206,7 +1206,7 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>4.83</v>
       </c>
       <c r="O16" t="n">
         <v>43.41</v>
@@ -1215,7 +1215,7 @@
         <v>11.81</v>
       </c>
       <c r="Q16" t="n">
-        <v>31.6</v>
+        <v>26.77</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -1250,7 +1250,7 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="O17" t="n">
         <v>41.54</v>
@@ -1259,7 +1259,7 @@
         <v>12.02</v>
       </c>
       <c r="Q17" t="n">
-        <v>29.52</v>
+        <v>24.37</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -1338,7 +1338,7 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="O19" t="n">
         <v>27.3</v>
@@ -1347,7 +1347,7 @@
         <v>11.96</v>
       </c>
       <c r="Q19" t="n">
-        <v>15.34</v>
+        <v>10.19</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -1467,7 +1467,7 @@
         </is>
       </c>
       <c r="M22" t="n">
-        <v>10.49</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -1482,7 +1482,7 @@
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>10.49</v>
       </c>
       <c r="S22" s="1">
         <f>T22/V$1</f>
@@ -1511,7 +1511,7 @@
         </is>
       </c>
       <c r="M23" t="n">
-        <v>10.15</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -1526,7 +1526,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>10.15</v>
       </c>
       <c r="S23" s="1">
         <f>T23/V$1</f>
@@ -1555,7 +1555,7 @@
         </is>
       </c>
       <c r="M24" t="n">
-        <v>7.09</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -1570,7 +1570,7 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>5</v>
+        <v>12.09</v>
       </c>
       <c r="S24" s="1">
         <f>T24/V$1</f>
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="M26" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -1658,7 +1658,7 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>6.54</v>
+        <v>8.43</v>
       </c>
       <c r="S26" s="1">
         <f>T26/V$1</f>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -1914,7 +1914,7 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>4.8</v>
+        <v>1.09</v>
       </c>
       <c r="S4" s="1">
         <f>T4/V$1</f>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -2002,7 +2002,7 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>6.84</v>
+        <v>6.83</v>
       </c>
       <c r="S6" s="1">
         <f>T6/V$1</f>
@@ -2073,8 +2073,8 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 1 (Time: 0.006s).
-vFinalCharge(360). vE_SinitPercentage(1000). vCharge("2023-08-22","0:00:00",0). vCharge("2023-08-22","10:00:00",0). vCharge("2023-08-22","11:00:00",0). vCharge("2023-08-22","12:00:00",0). vCharge("2023-08-22","13:00:00",0). vCharge("2023-08-22","14:00:00",0). vCharge("2023-08-22","15:00:00",0). vCharge("2023-08-22","16:00:00",168). vCharge("2023-08-22","17:00:00",236). vCharge("2023-08-22","18:00:00",0). vCharge("2023-08-22","19:00:00",0). vCharge("2023-08-22","1:00:00",0). vCharge("2023-08-22","20:00:00",0). vCharge("2023-08-22","21:00:00",0). vCharge("2023-08-22","22:00:00",0). vCharge("2023-08-22","23:00:00",0). vCharge("2023-08-22","2:00:00",0). vCharge("2023-08-22","3:00:00",0). vCharge("2023-08-22","4:00:00",0). vCharge("2023-08-22","5:00:00",0). vCharge("2023-08-22","6:00:00",0). vCharge("2023-08-22","7:00:00",0). vCharge("2023-08-22","8:00:00",888). vCharge("2023-08-22","9:00:00",0). vDischarge("2023-08-22","0:00:00",0). vDischarge("2023-08-22","10:00:00",0). vDischarge("2023-08-22","11:00:00",0). vDischarge("2023-08-22","12:00:00",0). vDischarge("2023-08-22","13:00:00",0). vDischarge("2023-08-22","14:00:00",0). vDischarge("2023-08-22","15:00:00",0). vDischarge("2023-08-22","16:00:00",0). vDischarge("2023-08-22","17:00:00",0). vDischarge("2023-08-22","18:00:00",0). vDischarge("2023-08-22","19:00:00",1100). vDischarge("2023-08-22","1:00:00",0). vDischarge("2023-08-22","20:00:00",0). vDischarge("2023-08-22","21:00:00",191). vDischarge("2023-08-22","22:00:00",0). vDischarge("2023-08-22","23:00:00",1). vDischarge("2023-08-22","2:00:00",0). vDischarge("2023-08-22","3:00:00",0). vDischarge("2023-08-22","4:00:00",0). vDischarge("2023-08-22","5:00:00",0). vDischarge("2023-08-22","6:00:00",0). vDischarge("2023-08-22","7:00:00",0). vDischarge("2023-08-22","8:00:00",0). vDischarge("2023-08-22","9:00:00",0). vFeed_in("2023-08-22","0:00:00",0). vFeed_in("2023-08-22","10:00:00",2367). vFeed_in("2023-08-22","11:00:00",3069). vFeed_in("2023-08-22","12:00:00",2885). vFeed_in("2023-08-22","13:00:00",3118). vFeed_in("2023-08-22","14:00:00",3066). vFeed_in("2023-08-22","15:00:00",2353). vFeed_in("2023-08-22","16:00:00",9). vFeed_in("2023-08-22","17:00:00",741). vFeed_in("2023-08-22","18:00:00",0). vFeed_in("2023-08-22","19:00:00",0). vFeed_in("2023-08-22","1:00:00",0). vFeed_in("2023-08-22","20:00:00",0). vFeed_in("2023-08-22","21:00:00",0). vFeed_in("2023-08-22","22:00:00",0). vFeed_in("2023-08-22","23:00:00",0). vFeed_in("2023-08-22","2:00:00",0). vFeed_in("2023-08-22","3:00:00",0). vFeed_in("2023-08-22","4:00:00",0). vFeed_in("2023-08-22","5:00:00",0). vFeed_in("2023-08-22","6:00:00",0). vFeed_in("2023-08-22","7:00:00",0). vFeed_in("2023-08-22","8:00:00",71). vFeed_in("2023-08-22","9:00:00",2047). vFrom_grid("2023-08-22","0:00:00",770). vFrom_grid("2023-08-22","10:00:00",0). vFrom_grid("2023-08-22","11:00:00",0). vFrom_grid("2023-08-22","12:00:00",0). vFrom_grid("2023-08-22","13:00:00",0). vFrom_grid("2023-08-22","14:00:00",0). vFrom_grid("2023-08-22","15:00:00",0). vFrom_grid("2023-08-22","16:00:00",0). vFrom_grid("2023-08-22","17:00:00",0). vFrom_grid("2023-08-22","18:00:00",292). vFrom_grid("2023-08-22","19:00:00",0). vFrom_grid("2023-08-22","1:00:00",480). vFrom_grid("2023-08-22","20:00:00",691). vFrom_grid("2023-08-22","21:00:00",851). vFrom_grid("2023-08-22","22:00:00",1108). vFrom_grid("2023-08-22","23:00:00",768). vFrom_grid("2023-08-22","2:00:00",720). vFrom_grid("2023-08-22","3:00:00",684). vFrom_grid("2023-08-22","4:00:00",663). vFrom_grid("2023-08-22","5:00:00",686). vFrom_grid("2023-08-22","6:00:00",623). vFrom_grid("2023-08-22","7:00:00",185). vFrom_grid("2023-08-22","8:00:00",0). vFrom_grid("2023-08-22","9:00:00",0). vP_L("2023-08-22","0:00:00",770). vP_L("2023-08-22","10:00:00",1166). vP_L("2023-08-22","11:00:00",832). vP_L("2023-08-22","12:00:00",1192). vP_L("2023-08-22","13:00:00",1194). vP_L("2023-08-22","14:00:00",1202). vP_L("2023-08-22","15:00:00",1212). vP_L("2023-08-22","16:00:00",1205). vP_L("2023-08-22","17:00:00",680). vP_L("2023-08-22","18:00:00",941). vP_L("2023-08-22","19:00:00",1208). vP_L("2023-08-22","1:00:00",480). vP_L("2023-08-22","20:00:00",691). vP_L("2023-08-22","21:00:00",1042). vP_L("2023-08-22","22:00:00",1108). vP_L("2023-08-22","23:00:00",769). vP_L("2023-08-22","2:00:00",720). vP_L("2023-08-22","3:00:00",684). vP_L("2023-08-22","4:00:00",663). vP_L("2023-08-22","5:00:00",686). vP_L("2023-08-22","6:00:00",682). vP_L("2023-08-22","7:00:00",680). vP_L("2023-08-22","8:00:00",680). vP_L("2023-08-22","9:00:00",683). vP_PV("2023-08-22","0:00:00",0). vP_PV("2023-08-22","10:00:00",3533). vP_PV("2023-08-22","11:00:00",3901). vP_PV("2023-08-22","12:00:00",4077). vP_PV("2023-08-22","13:00:00",4312). vP_PV("2023-08-22","14:00:00",4268). vP_PV("2023-08-22","15:00:00",3565). vP_PV("2023-08-22","16:00:00",1382). vP_PV("2023-08-22","17:00:00",1657). vP_PV("2023-08-22","18:00:00",649). vP_PV("2023-08-22","19:00:00",108). vP_PV("2023-08-22","1:00:00",0). vP_PV("2023-08-22","20:00:00",0). vP_PV("2023-08-22","21:00:00",0). vP_PV("2023-08-22","22:00:00",0). vP_PV("2023-08-22","23:00:00",0). vP_PV("2023-08-22","2:00:00",0). vP_PV("2023-08-22","3:00:00",0). vP_PV("2023-08-22","4:00:00",0). vP_PV("2023-08-22","5:00:00",0). vP_PV("2023-08-22","6:00:00",59). vP_PV("2023-08-22","7:00:00",495). vP_PV("2023-08-22","8:00:00",1639). vP_PV("2023-08-22","9:00:00",2730).
+          <t xml:space="preserve"> 1 (Time: 0.005s).
+vFinalCharge(3600). vE_SinitPercentage(10000). vCharge("2023-08-22","0:00:00",0). vCharge("2023-08-22","10:00:00",0). vCharge("2023-08-22","11:00:00",0). vCharge("2023-08-22","12:00:00",0). vCharge("2023-08-22","13:00:00",0). vCharge("2023-08-22","14:00:00",0). vCharge("2023-08-22","15:00:00",346). vCharge("2023-08-22","16:00:00",0). vCharge("2023-08-22","17:00:00",1). vCharge("2023-08-22","18:00:00",0). vCharge("2023-08-22","19:00:00",0). vCharge("2023-08-22","1:00:00",0). vCharge("2023-08-22","20:00:00",0). vCharge("2023-08-22","21:00:00",0). vCharge("2023-08-22","22:00:00",0). vCharge("2023-08-22","23:00:00",0). vCharge("2023-08-22","2:00:00",0). vCharge("2023-08-22","3:00:00",0). vCharge("2023-08-22","4:00:00",0). vCharge("2023-08-22","5:00:00",0). vCharge("2023-08-22","6:00:00",0). vCharge("2023-08-22","7:00:00",0). vCharge("2023-08-22","8:00:00",537). vCharge("2023-08-22","9:00:00",0). vDischarge("2023-08-22","0:00:00",0). vDischarge("2023-08-22","10:00:00",0). vDischarge("2023-08-22","11:00:00",0). vDischarge("2023-08-22","12:00:00",0). vDischarge("2023-08-22","13:00:00",0). vDischarge("2023-08-22","14:00:00",0). vDischarge("2023-08-22","15:00:00",0). vDischarge("2023-08-22","16:00:00",0). vDischarge("2023-08-22","17:00:00",0). vDischarge("2023-08-22","18:00:00",0). vDischarge("2023-08-22","19:00:00",0). vDischarge("2023-08-22","1:00:00",371). vDischarge("2023-08-22","20:00:00",0). vDischarge("2023-08-22","21:00:00",0). vDischarge("2023-08-22","22:00:00",0). vDischarge("2023-08-22","23:00:00",0). vDischarge("2023-08-22","2:00:00",0). vDischarge("2023-08-22","3:00:00",1). vDischarge("2023-08-22","4:00:00",0). vDischarge("2023-08-22","5:00:00",147). vDischarge("2023-08-22","6:00:00",363). vDischarge("2023-08-22","7:00:00",2). vDischarge("2023-08-22","8:00:00",0). vDischarge("2023-08-22","9:00:00",0). vFeed_in("2023-08-22","0:00:00",0). vFeed_in("2023-08-22","10:00:00",2367). vFeed_in("2023-08-22","11:00:00",3069). vFeed_in("2023-08-22","12:00:00",2885). vFeed_in("2023-08-22","13:00:00",3118). vFeed_in("2023-08-22","14:00:00",3066). vFeed_in("2023-08-22","15:00:00",2007). vFeed_in("2023-08-22","16:00:00",177). vFeed_in("2023-08-22","17:00:00",976). vFeed_in("2023-08-22","18:00:00",0). vFeed_in("2023-08-22","19:00:00",0). vFeed_in("2023-08-22","1:00:00",0). vFeed_in("2023-08-22","20:00:00",0). vFeed_in("2023-08-22","21:00:00",0). vFeed_in("2023-08-22","22:00:00",0). vFeed_in("2023-08-22","23:00:00",0). vFeed_in("2023-08-22","2:00:00",0). vFeed_in("2023-08-22","3:00:00",0). vFeed_in("2023-08-22","4:00:00",0). vFeed_in("2023-08-22","5:00:00",0). vFeed_in("2023-08-22","6:00:00",0). vFeed_in("2023-08-22","7:00:00",0). vFeed_in("2023-08-22","8:00:00",422). vFeed_in("2023-08-22","9:00:00",2047). vFrom_grid("2023-08-22","0:00:00",770). vFrom_grid("2023-08-22","10:00:00",0). vFrom_grid("2023-08-22","11:00:00",0). vFrom_grid("2023-08-22","12:00:00",0). vFrom_grid("2023-08-22","13:00:00",0). vFrom_grid("2023-08-22","14:00:00",0). vFrom_grid("2023-08-22","15:00:00",0). vFrom_grid("2023-08-22","16:00:00",0). vFrom_grid("2023-08-22","17:00:00",0). vFrom_grid("2023-08-22","18:00:00",292). vFrom_grid("2023-08-22","19:00:00",1100). vFrom_grid("2023-08-22","1:00:00",109). vFrom_grid("2023-08-22","20:00:00",691). vFrom_grid("2023-08-22","21:00:00",1042). vFrom_grid("2023-08-22","22:00:00",1108). vFrom_grid("2023-08-22","23:00:00",769). vFrom_grid("2023-08-22","2:00:00",720). vFrom_grid("2023-08-22","3:00:00",683). vFrom_grid("2023-08-22","4:00:00",663). vFrom_grid("2023-08-22","5:00:00",539). vFrom_grid("2023-08-22","6:00:00",260). vFrom_grid("2023-08-22","7:00:00",183). vFrom_grid("2023-08-22","8:00:00",0). vFrom_grid("2023-08-22","9:00:00",0). vP_L("2023-08-22","0:00:00",770). vP_L("2023-08-22","10:00:00",1166). vP_L("2023-08-22","11:00:00",832). vP_L("2023-08-22","12:00:00",1192). vP_L("2023-08-22","13:00:00",1194). vP_L("2023-08-22","14:00:00",1202). vP_L("2023-08-22","15:00:00",1212). vP_L("2023-08-22","16:00:00",1205). vP_L("2023-08-22","17:00:00",680). vP_L("2023-08-22","18:00:00",941). vP_L("2023-08-22","19:00:00",1208). vP_L("2023-08-22","1:00:00",480). vP_L("2023-08-22","20:00:00",691). vP_L("2023-08-22","21:00:00",1042). vP_L("2023-08-22","22:00:00",1108). vP_L("2023-08-22","23:00:00",769). vP_L("2023-08-22","2:00:00",720). vP_L("2023-08-22","3:00:00",684). vP_L("2023-08-22","4:00:00",663). vP_L("2023-08-22","5:00:00",686). vP_L("2023-08-22","6:00:00",682). vP_L("2023-08-22","7:00:00",680). vP_L("2023-08-22","8:00:00",680). vP_L("2023-08-22","9:00:00",683). vP_PV("2023-08-22","0:00:00",0). vP_PV("2023-08-22","10:00:00",3533). vP_PV("2023-08-22","11:00:00",3901). vP_PV("2023-08-22","12:00:00",4077). vP_PV("2023-08-22","13:00:00",4312). vP_PV("2023-08-22","14:00:00",4268). vP_PV("2023-08-22","15:00:00",3565). vP_PV("2023-08-22","16:00:00",1382). vP_PV("2023-08-22","17:00:00",1657). vP_PV("2023-08-22","18:00:00",649). vP_PV("2023-08-22","19:00:00",108). vP_PV("2023-08-22","1:00:00",0). vP_PV("2023-08-22","20:00:00",0). vP_PV("2023-08-22","21:00:00",0). vP_PV("2023-08-22","22:00:00",0). vP_PV("2023-08-22","23:00:00",0). vP_PV("2023-08-22","2:00:00",0). vP_PV("2023-08-22","3:00:00",0). vP_PV("2023-08-22","4:00:00",0). vP_PV("2023-08-22","5:00:00",0). vP_PV("2023-08-22","6:00:00",59). vP_PV("2023-08-22","7:00:00",495). vP_PV("2023-08-22","8:00:00",1639). vP_PV("2023-08-22","9:00:00",2730).
 </t>
         </is>
       </c>
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -2112,7 +2112,7 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>6.86</v>
+        <v>5.39</v>
       </c>
       <c r="S8" s="1">
         <f>T8/V$1</f>
@@ -2128,7 +2128,7 @@
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.006</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="9">
@@ -2149,7 +2149,7 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -2164,7 +2164,7 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>6.23</v>
+        <v>2.6</v>
       </c>
       <c r="S9" s="1">
         <f>T9/V$1</f>
@@ -2202,7 +2202,7 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -2217,7 +2217,7 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="S10" s="1">
         <f>T10/V$1</f>
@@ -2249,7 +2249,7 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>8.880000000000001</v>
+        <v>5.37</v>
       </c>
       <c r="O11" t="n">
         <v>16.39</v>
@@ -2258,7 +2258,7 @@
         <v>6.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.71</v>
+        <v>4.22</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -2557,7 +2557,7 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="O18" t="n">
         <v>35.65</v>
@@ -2566,7 +2566,7 @@
         <v>12.12</v>
       </c>
       <c r="Q18" t="n">
-        <v>23.53</v>
+        <v>20.07</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2601,7 +2601,7 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>13.82</v>
@@ -2610,7 +2610,7 @@
         <v>12.05</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.09</v>
+        <v>1.77</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2645,7 +2645,7 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>2.36</v>
+        <v>0.01</v>
       </c>
       <c r="O20" t="n">
         <v>16.57</v>
@@ -2654,7 +2654,7 @@
         <v>6.8</v>
       </c>
       <c r="Q20" t="n">
-        <v>7.41</v>
+        <v>9.76</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -2730,7 +2730,7 @@
         </is>
       </c>
       <c r="M22" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -2745,7 +2745,7 @@
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="S22" s="1">
         <f>T22/V$1</f>
@@ -2818,7 +2818,7 @@
         </is>
       </c>
       <c r="M24" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -2833,7 +2833,7 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>8.51</v>
+        <v>10.42</v>
       </c>
       <c r="S24" s="1">
         <f>T24/V$1</f>
@@ -2906,7 +2906,7 @@
         </is>
       </c>
       <c r="M26" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -2921,7 +2921,7 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>7.68</v>
+        <v>7.69</v>
       </c>
       <c r="S26" s="1">
         <f>T26/V$1</f>
@@ -3108,7 +3108,7 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -3123,7 +3123,7 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>7.84</v>
+        <v>7.81</v>
       </c>
       <c r="S3" s="1">
         <f>T3/V$1</f>
@@ -3162,7 +3162,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>6.79</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -3177,7 +3177,7 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>7.07</v>
+        <v>0.28</v>
       </c>
       <c r="S4" s="1">
         <f>T4/V$1</f>
@@ -3206,7 +3206,7 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>5.39</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -3221,7 +3221,7 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>5.96</v>
+        <v>0.57</v>
       </c>
       <c r="S5" s="1">
         <f>T5/V$1</f>
@@ -3250,7 +3250,7 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -3265,7 +3265,7 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>6.3</v>
+        <v>1</v>
       </c>
       <c r="S6" s="1">
         <f>T6/V$1</f>
@@ -3304,7 +3304,7 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -3319,7 +3319,7 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>6.72</v>
+        <v>5.11</v>
       </c>
       <c r="S7" s="1">
         <f>T7/V$1</f>
@@ -3336,8 +3336,8 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 1 (Time: 0.006s).
-vFinalCharge(360). vE_SinitPercentage(1000). vCharge("2023-08-23","0:00:00",0). vCharge("2023-08-23","10:00:00",0). vCharge("2023-08-23","11:00:00",0). vCharge("2023-08-23","12:00:00",0). vCharge("2023-08-23","13:00:00",0). vCharge("2023-08-23","14:00:00",2). vCharge("2023-08-23","15:00:00",0). vCharge("2023-08-23","16:00:00",1). vCharge("2023-08-23","17:00:00",0). vCharge("2023-08-23","18:00:00",0). vCharge("2023-08-23","19:00:00",0). vCharge("2023-08-23","1:00:00",0). vCharge("2023-08-23","20:00:00",0). vCharge("2023-08-23","21:00:00",0). vCharge("2023-08-23","22:00:00",0). vCharge("2023-08-23","23:00:00",0). vCharge("2023-08-23","2:00:00",0). vCharge("2023-08-23","3:00:00",0). vCharge("2023-08-23","4:00:00",0). vCharge("2023-08-23","5:00:00",0). vCharge("2023-08-23","6:00:00",0). vCharge("2023-08-23","7:00:00",0). vCharge("2023-08-23","8:00:00",0). vCharge("2023-08-23","9:00:00",0). vDischarge("2023-08-23","0:00:00",0). vDischarge("2023-08-23","10:00:00",0). vDischarge("2023-08-23","11:00:00",0). vDischarge("2023-08-23","12:00:00",0). vDischarge("2023-08-23","13:00:00",0). vDischarge("2023-08-23","14:00:00",0). vDischarge("2023-08-23","15:00:00",0). vDischarge("2023-08-23","16:00:00",0). vDischarge("2023-08-23","17:00:00",0). vDischarge("2023-08-23","18:00:00",1). vDischarge("2023-08-23","19:00:00",0). vDischarge("2023-08-23","1:00:00",0). vDischarge("2023-08-23","20:00:00",0). vDischarge("2023-08-23","21:00:00",0). vDischarge("2023-08-23","22:00:00",1). vDischarge("2023-08-23","23:00:00",1). vDischarge("2023-08-23","2:00:00",0). vDischarge("2023-08-23","3:00:00",0). vDischarge("2023-08-23","4:00:00",0). vDischarge("2023-08-23","5:00:00",0). vDischarge("2023-08-23","6:00:00",0). vDischarge("2023-08-23","7:00:00",0). vDischarge("2023-08-23","8:00:00",0). vDischarge("2023-08-23","9:00:00",0). vFeed_in("2023-08-23","0:00:00",0). vFeed_in("2023-08-23","10:00:00",2887). vFeed_in("2023-08-23","11:00:00",3057). vFeed_in("2023-08-23","12:00:00",1981). vFeed_in("2023-08-23","13:00:00",2023). vFeed_in("2023-08-23","14:00:00",1783). vFeed_in("2023-08-23","15:00:00",977). vFeed_in("2023-08-23","16:00:00",321). vFeed_in("2023-08-23","17:00:00",219). vFeed_in("2023-08-23","18:00:00",0). vFeed_in("2023-08-23","19:00:00",0). vFeed_in("2023-08-23","1:00:00",0). vFeed_in("2023-08-23","20:00:00",0). vFeed_in("2023-08-23","21:00:00",0). vFeed_in("2023-08-23","22:00:00",0). vFeed_in("2023-08-23","23:00:00",0). vFeed_in("2023-08-23","2:00:00",0). vFeed_in("2023-08-23","3:00:00",0). vFeed_in("2023-08-23","4:00:00",0). vFeed_in("2023-08-23","5:00:00",0). vFeed_in("2023-08-23","6:00:00",0). vFeed_in("2023-08-23","7:00:00",0). vFeed_in("2023-08-23","8:00:00",1059). vFeed_in("2023-08-23","9:00:00",2076). vFrom_grid("2023-08-23","0:00:00",784). vFrom_grid("2023-08-23","10:00:00",0). vFrom_grid("2023-08-23","11:00:00",0). vFrom_grid("2023-08-23","12:00:00",0). vFrom_grid("2023-08-23","13:00:00",0). vFrom_grid("2023-08-23","14:00:00",0). vFrom_grid("2023-08-23","15:00:00",0). vFrom_grid("2023-08-23","16:00:00",0). vFrom_grid("2023-08-23","17:00:00",0). vFrom_grid("2023-08-23","18:00:00",702). vFrom_grid("2023-08-23","19:00:00",1172). vFrom_grid("2023-08-23","1:00:00",707). vFrom_grid("2023-08-23","20:00:00",1176). vFrom_grid("2023-08-23","21:00:00",1221). vFrom_grid("2023-08-23","22:00:00",677). vFrom_grid("2023-08-23","23:00:00",848). vFrom_grid("2023-08-23","2:00:00",596). vFrom_grid("2023-08-23","3:00:00",630). vFrom_grid("2023-08-23","4:00:00",672). vFrom_grid("2023-08-23","5:00:00",701). vFrom_grid("2023-08-23","6:00:00",674). vFrom_grid("2023-08-23","7:00:00",214). vFrom_grid("2023-08-23","8:00:00",0). vFrom_grid("2023-08-23","9:00:00",0). vP_L("2023-08-23","0:00:00",784). vP_L("2023-08-23","10:00:00",682). vP_L("2023-08-23","11:00:00",928). vP_L("2023-08-23","12:00:00",1192). vP_L("2023-08-23","13:00:00",1197). vP_L("2023-08-23","14:00:00",1239). vP_L("2023-08-23","15:00:00",1203). vP_L("2023-08-23","16:00:00",1202). vP_L("2023-08-23","17:00:00",1192). vP_L("2023-08-23","18:00:00",1211). vP_L("2023-08-23","19:00:00",1211). vP_L("2023-08-23","1:00:00",707). vP_L("2023-08-23","20:00:00",1176). vP_L("2023-08-23","21:00:00",1221). vP_L("2023-08-23","22:00:00",678). vP_L("2023-08-23","23:00:00",849). vP_L("2023-08-23","2:00:00",596). vP_L("2023-08-23","3:00:00",630). vP_L("2023-08-23","4:00:00",672). vP_L("2023-08-23","5:00:00",701). vP_L("2023-08-23","6:00:00",691). vP_L("2023-08-23","7:00:00",681). vP_L("2023-08-23","8:00:00",548). vP_L("2023-08-23","9:00:00",704). vP_PV("2023-08-23","0:00:00",0). vP_PV("2023-08-23","10:00:00",3569). vP_PV("2023-08-23","11:00:00",3985). vP_PV("2023-08-23","12:00:00",3173). vP_PV("2023-08-23","13:00:00",3220). vP_PV("2023-08-23","14:00:00",3024). vP_PV("2023-08-23","15:00:00",2180). vP_PV("2023-08-23","16:00:00",1524). vP_PV("2023-08-23","17:00:00",1411). vP_PV("2023-08-23","18:00:00",508). vP_PV("2023-08-23","19:00:00",39). vP_PV("2023-08-23","1:00:00",0). vP_PV("2023-08-23","20:00:00",0). vP_PV("2023-08-23","21:00:00",0). vP_PV("2023-08-23","22:00:00",0). vP_PV("2023-08-23","23:00:00",0). vP_PV("2023-08-23","2:00:00",0). vP_PV("2023-08-23","3:00:00",0). vP_PV("2023-08-23","4:00:00",0). vP_PV("2023-08-23","5:00:00",0). vP_PV("2023-08-23","6:00:00",17). vP_PV("2023-08-23","7:00:00",467). vP_PV("2023-08-23","8:00:00",1607). vP_PV("2023-08-23","9:00:00",2780).
+          <t xml:space="preserve"> 1 (Time: 0.008s).
+vFinalCharge(3600). vE_SinitPercentage(10000). vCharge("2023-08-23","0:00:00",0). vCharge("2023-08-23","10:00:00",23). vCharge("2023-08-23","11:00:00",1702). vCharge("2023-08-23","12:00:00",26). vCharge("2023-08-23","13:00:00",15). vCharge("2023-08-23","14:00:00",1). vCharge("2023-08-23","15:00:00",329). vCharge("2023-08-23","16:00:00",1). vCharge("2023-08-23","17:00:00",3). vCharge("2023-08-23","18:00:00",0). vCharge("2023-08-23","19:00:00",0). vCharge("2023-08-23","1:00:00",0). vCharge("2023-08-23","20:00:00",0). vCharge("2023-08-23","21:00:00",0). vCharge("2023-08-23","22:00:00",0). vCharge("2023-08-23","23:00:00",0). vCharge("2023-08-23","2:00:00",0). vCharge("2023-08-23","3:00:00",0). vCharge("2023-08-23","4:00:00",0). vCharge("2023-08-23","5:00:00",0). vCharge("2023-08-23","6:00:00",0). vCharge("2023-08-23","7:00:00",0). vCharge("2023-08-23","8:00:00",5). vCharge("2023-08-23","9:00:00",0). vDischarge("2023-08-23","0:00:00",3). vDischarge("2023-08-23","10:00:00",0). vDischarge("2023-08-23","11:00:00",0). vDischarge("2023-08-23","12:00:00",0). vDischarge("2023-08-23","13:00:00",0). vDischarge("2023-08-23","14:00:00",0). vDischarge("2023-08-23","15:00:00",0). vDischarge("2023-08-23","16:00:00",0). vDischarge("2023-08-23","17:00:00",0). vDischarge("2023-08-23","18:00:00",0). vDischarge("2023-08-23","19:00:00",0). vDischarge("2023-08-23","1:00:00",679). vDischarge("2023-08-23","20:00:00",0). vDischarge("2023-08-23","21:00:00",0). vDischarge("2023-08-23","22:00:00",0). vDischarge("2023-08-23","23:00:00",0). vDischarge("2023-08-23","2:00:00",539). vDischarge("2023-08-23","3:00:00",530). vDischarge("2023-08-23","4:00:00",161). vDischarge("2023-08-23","5:00:00",3). vDischarge("2023-08-23","6:00:00",190). vDischarge("2023-08-23","7:00:00",0). vDischarge("2023-08-23","8:00:00",0). vDischarge("2023-08-23","9:00:00",0). vFeed_in("2023-08-23","0:00:00",0). vFeed_in("2023-08-23","10:00:00",2864). vFeed_in("2023-08-23","11:00:00",1355). vFeed_in("2023-08-23","12:00:00",1955). vFeed_in("2023-08-23","13:00:00",2008). vFeed_in("2023-08-23","14:00:00",1784). vFeed_in("2023-08-23","15:00:00",648). vFeed_in("2023-08-23","16:00:00",321). vFeed_in("2023-08-23","17:00:00",216). vFeed_in("2023-08-23","18:00:00",0). vFeed_in("2023-08-23","19:00:00",0). vFeed_in("2023-08-23","1:00:00",0). vFeed_in("2023-08-23","20:00:00",0). vFeed_in("2023-08-23","21:00:00",0). vFeed_in("2023-08-23","22:00:00",0). vFeed_in("2023-08-23","23:00:00",0). vFeed_in("2023-08-23","2:00:00",0). vFeed_in("2023-08-23","3:00:00",0). vFeed_in("2023-08-23","4:00:00",0). vFeed_in("2023-08-23","5:00:00",0). vFeed_in("2023-08-23","6:00:00",0). vFeed_in("2023-08-23","7:00:00",0). vFeed_in("2023-08-23","8:00:00",1054). vFeed_in("2023-08-23","9:00:00",2076). vFrom_grid("2023-08-23","0:00:00",781). vFrom_grid("2023-08-23","10:00:00",0). vFrom_grid("2023-08-23","11:00:00",0). vFrom_grid("2023-08-23","12:00:00",0). vFrom_grid("2023-08-23","13:00:00",0). vFrom_grid("2023-08-23","14:00:00",0). vFrom_grid("2023-08-23","15:00:00",0). vFrom_grid("2023-08-23","16:00:00",0). vFrom_grid("2023-08-23","17:00:00",0). vFrom_grid("2023-08-23","18:00:00",703). vFrom_grid("2023-08-23","19:00:00",1172). vFrom_grid("2023-08-23","1:00:00",28). vFrom_grid("2023-08-23","20:00:00",1176). vFrom_grid("2023-08-23","21:00:00",1221). vFrom_grid("2023-08-23","22:00:00",678). vFrom_grid("2023-08-23","23:00:00",849). vFrom_grid("2023-08-23","2:00:00",57). vFrom_grid("2023-08-23","3:00:00",100). vFrom_grid("2023-08-23","4:00:00",511). vFrom_grid("2023-08-23","5:00:00",698). vFrom_grid("2023-08-23","6:00:00",484). vFrom_grid("2023-08-23","7:00:00",214). vFrom_grid("2023-08-23","8:00:00",0). vFrom_grid("2023-08-23","9:00:00",0). vP_L("2023-08-23","0:00:00",784). vP_L("2023-08-23","10:00:00",682). vP_L("2023-08-23","11:00:00",928). vP_L("2023-08-23","12:00:00",1192). vP_L("2023-08-23","13:00:00",1197). vP_L("2023-08-23","14:00:00",1239). vP_L("2023-08-23","15:00:00",1203). vP_L("2023-08-23","16:00:00",1202). vP_L("2023-08-23","17:00:00",1192). vP_L("2023-08-23","18:00:00",1211). vP_L("2023-08-23","19:00:00",1211). vP_L("2023-08-23","1:00:00",707). vP_L("2023-08-23","20:00:00",1176). vP_L("2023-08-23","21:00:00",1221). vP_L("2023-08-23","22:00:00",678). vP_L("2023-08-23","23:00:00",849). vP_L("2023-08-23","2:00:00",596). vP_L("2023-08-23","3:00:00",630). vP_L("2023-08-23","4:00:00",672). vP_L("2023-08-23","5:00:00",701). vP_L("2023-08-23","6:00:00",691). vP_L("2023-08-23","7:00:00",681). vP_L("2023-08-23","8:00:00",548). vP_L("2023-08-23","9:00:00",704). vP_PV("2023-08-23","0:00:00",0). vP_PV("2023-08-23","10:00:00",3569). vP_PV("2023-08-23","11:00:00",3985). vP_PV("2023-08-23","12:00:00",3173). vP_PV("2023-08-23","13:00:00",3220). vP_PV("2023-08-23","14:00:00",3024). vP_PV("2023-08-23","15:00:00",2180). vP_PV("2023-08-23","16:00:00",1524). vP_PV("2023-08-23","17:00:00",1411). vP_PV("2023-08-23","18:00:00",508). vP_PV("2023-08-23","19:00:00",39). vP_PV("2023-08-23","1:00:00",0). vP_PV("2023-08-23","20:00:00",0). vP_PV("2023-08-23","21:00:00",0). vP_PV("2023-08-23","22:00:00",0). vP_PV("2023-08-23","23:00:00",0). vP_PV("2023-08-23","2:00:00",0). vP_PV("2023-08-23","3:00:00",0). vP_PV("2023-08-23","4:00:00",0). vP_PV("2023-08-23","5:00:00",0). vP_PV("2023-08-23","6:00:00",17). vP_PV("2023-08-23","7:00:00",467). vP_PV("2023-08-23","8:00:00",1607). vP_PV("2023-08-23","9:00:00",2780).
 </t>
         </is>
       </c>
@@ -3360,7 +3360,7 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -3375,7 +3375,7 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>7.01</v>
+        <v>6.98</v>
       </c>
       <c r="S8" s="1">
         <f>T8/V$1</f>
@@ -3391,7 +3391,7 @@
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.006</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="9">
@@ -3412,7 +3412,7 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -3427,7 +3427,7 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>6.74</v>
+        <v>4.84</v>
       </c>
       <c r="S9" s="1">
         <f>T9/V$1</f>
@@ -3512,7 +3512,7 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="O11" t="n">
         <v>16.07</v>
@@ -3521,7 +3521,7 @@
         <v>5.48</v>
       </c>
       <c r="Q11" t="n">
-        <v>10.59</v>
+        <v>10.54</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="O13" t="n">
         <v>35.69</v>
@@ -3609,7 +3609,7 @@
         <v>6.82</v>
       </c>
       <c r="Q13" t="n">
-        <v>28.87</v>
+        <v>28.64</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3644,7 +3644,7 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>17.02</v>
       </c>
       <c r="O14" t="n">
         <v>39.85</v>
@@ -3653,7 +3653,7 @@
         <v>9.279999999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>30.57</v>
+        <v>13.55</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -3688,7 +3688,7 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="O15" t="n">
         <v>31.73</v>
@@ -3697,7 +3697,7 @@
         <v>11.92</v>
       </c>
       <c r="Q15" t="n">
-        <v>19.81</v>
+        <v>19.55</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -3732,7 +3732,7 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="O16" t="n">
         <v>32.2</v>
@@ -3741,7 +3741,7 @@
         <v>11.97</v>
       </c>
       <c r="Q16" t="n">
-        <v>20.23</v>
+        <v>20.08</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -3776,7 +3776,7 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="O17" t="n">
         <v>30.24</v>
@@ -3785,7 +3785,7 @@
         <v>12.39</v>
       </c>
       <c r="Q17" t="n">
-        <v>17.83</v>
+        <v>17.84</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -3820,7 +3820,7 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="O18" t="n">
         <v>21.8</v>
@@ -3829,7 +3829,7 @@
         <v>12.03</v>
       </c>
       <c r="Q18" t="n">
-        <v>9.77</v>
+        <v>6.48</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -3908,7 +3908,7 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="O20" t="n">
         <v>14.11</v>
@@ -3917,7 +3917,7 @@
         <v>11.92</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.19</v>
+        <v>2.16</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="M21" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -3964,7 +3964,7 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>7.02</v>
+        <v>7.03</v>
       </c>
       <c r="S21" s="1">
         <f>T21/V$1</f>
@@ -4125,7 +4125,7 @@
         </is>
       </c>
       <c r="M25" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -4140,7 +4140,7 @@
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>6.77</v>
+        <v>6.78</v>
       </c>
       <c r="S25" s="1">
         <f>T25/V$1</f>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="M26" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -4184,7 +4184,7 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>8.48</v>
+        <v>8.49</v>
       </c>
       <c r="S26" s="1">
         <f>T26/V$1</f>
